--- a/editorial/title-plan-1482/seo-tieu-de-03-494.xlsx
+++ b/editorial/title-plan-1482/seo-tieu-de-03-494.xlsx
@@ -33378,120 +33378,276 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">QUY TẮC</t>
+          <t xml:space="preserve">BƯỚC / QUY TẮC</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">HƯỚNG DẪN</t>
+          <t xml:space="preserve">AI ĐỌC VÀ LÀM ĐÚNG NGAY</t>
         </is>
       </c>
     </row>
     <row r="2" ht="23" customHeight="1">
       <c r="A2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nguồn sự thật</t>
+          <t xml:space="preserve">0. Đọc nhanh</t>
         </is>
       </c>
       <c r="B2" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">plan.json là hàng đợi; bảng Excel được tạo lại sau cập nhật G7</t>
+          <t xml:space="preserve">SOP: docs/TITLE-PLAN-1482-SOP.md; không quét lại toàn repo</t>
         </is>
       </c>
     </row>
     <row r="3" ht="23" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEO</t>
+          <t xml:space="preserve">1. Chọn 1–3 đề</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Không sản sinh thêm tiêu đề có cụm Thuê xe máy Hà Nội</t>
+          <t xml:space="preserve">Đọc plan.json hoặc chạy python scripts/title_plan_next.py --limit 3</t>
         </is>
       </c>
     </row>
     <row r="4" ht="23" customHeight="1">
       <c r="A4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Danh mục</t>
+          <t xml:space="preserve">2. TP không là NT</t>
         </is>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dùng Term ID cha con có thật; không tạo chuyên mục mới</t>
+          <t xml:space="preserve">TP-XXXX chỉ là đề tài; chưa Research PASS thì CHƯA được nhận Writer</t>
         </is>
       </c>
     </row>
     <row r="5" ht="23" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">51 phường</t>
+          <t xml:space="preserve">3. So trùng</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Giữ riêng chiến dịch 51 phường (Term 182) để không trùng</t>
+          <t xml:space="preserve">So URL, slug, intent với WordPress và data/topics.jsonl mới nhất</t>
         </is>
       </c>
     </row>
     <row r="6" ht="23" customHeight="1">
       <c r="A6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nghiên cứu</t>
+          <t xml:space="preserve">4. Chọn danh mục</t>
         </is>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tìm và đối chiếu 1-4 trang nguồn cho mỗi tiêu đề</t>
+          <t xml:space="preserve">Đúng Term ID và parent ở data/taxonomy.json; không tạo mục mới</t>
         </is>
       </c>
     </row>
     <row r="7" ht="23" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Luật</t>
+          <t xml:space="preserve">5. Đọc nguồn</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bất kỳ khẳng định pháp luật nào đều cần nguồn chính thức</t>
+          <t xml:space="preserve">Tìm 1–4 URL HTTPS thật, ghi chứng cứ nguồn và thời điểm</t>
         </is>
       </c>
     </row>
     <row r="8" ht="23" customHeight="1">
       <c r="A8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">QA</t>
+          <t xml:space="preserve">6. Chủ đề luật</t>
         </is>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Writer và Publisher giữ QA &gt;=85; không thay đổi các cổng</t>
+          <t xml:space="preserve">GPLX/độ tuổi/luật phải tra nguồn nhà nước đang hiệu lực</t>
         </is>
       </c>
     </row>
     <row r="9" ht="23" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Đã đăng</t>
+          <t xml:space="preserve">7. Giá/xe</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chỉ xác nhận khi ledger có phase VERIFIED và G7 PASS</t>
+          <t xml:space="preserve">NAP, giá, cọc theo data/business-facts.json; thông số theo hãng</t>
         </is>
       </c>
     </row>
     <row r="10" ht="23" customHeight="1">
       <c r="A10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cũ</t>
+          <t xml:space="preserve">8. Research QA</t>
         </is>
       </c>
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trước mỗi bài phải rà soát WP và kho chủ đề để chống trùng</t>
+          <t xml:space="preserve">Ứng viên qua Topic Factory/Research QA → NT-XXXXXX PLANNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="23" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9. W1–W9</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Claim slot auto hợp lệ; không cướp lease hoặc nhận NT chưa PLANNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="23" customHeight="1">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10. Viết bài</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.600–5.000 từ, intent riêng, 4+ H2, nguồn/internal link thật</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="23" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11. QA</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SEO ≥85 + Quality ≥85 + G1–G6 PASS mới đủ điều kiện Publisher</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="23" customHeight="1">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12. Publisher</t>
+        </is>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chỉ Publisher được WordPress POST; đúng danh mục, chống trùng</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="23" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13. Xác minh G7</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chỉ G7 VERIFIED + PASS đầy đủ mới đánh dấu PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="23" customHeight="1">
+      <c r="A16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14. URL sạch</t>
+        </is>
+      </c>
+      <c r="B16" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Slug theo tiêu đề; CẤM excel/xlsx/csv/tên file/TP-ID lọt vào URL</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="23" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15. SEO chính</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Không tạo thêm nhiều bài trùng từ khóa thuê xe máy Hà Nội</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="23" customHeight="1">
+      <c r="A18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16. 51 phường</t>
+        </is>
+      </c>
+      <c r="B18" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Giữ campaign phường ở Term 182 riêng, tránh nhân bản bài cũ</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="23" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17. Mất mạng</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lưu TP/NT/session/slot/branch/commit/step; resume, không bắt đầu lại</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="23" customHeight="1">
+      <c r="A20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">18. Nguồn sự thật</t>
+        </is>
+      </c>
+      <c r="B20" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Excel để xem; plan.json để chọn; Topic Registry và G7 để kiểm trạng thái</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="23" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19. Khi bị chặn</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">REVIEW/HOLD/NEEDS_RECONCILE; không bịa QA hoặc POST lại mù</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="23" customHeight="1">
+      <c r="A22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20. Báo cáo</t>
+        </is>
+      </c>
+      <c r="B22" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TP-ID / NT-ID / QA / WordPress ID / URL công khai / lỗi thật</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="23" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LỆNH NGẮN AI</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Đọc SOP; lấy 3 TP; so trùng; nghiên cứu 1–4 nguồn; Research QA; Writer QA; G7</t>
         </is>
       </c>
     </row>

--- a/editorial/title-plan-1482/seo-tieu-de-03-494.xlsx
+++ b/editorial/title-plan-1482/seo-tieu-de-03-494.xlsx
@@ -17060,9 +17060,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M253" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M253" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N253" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-091240</t>
+        </is>
+      </c>
+      <c r="O253" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4754</t>
+        </is>
+      </c>
+      <c r="P253" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/mang-vali-len-xe-buyt-ha-noi-duoc-khong-10-kg-va-30x40x60-cm-tuyen-san-bay-va-lien-tinh-duoc-20-kg/</t>
+        </is>
+      </c>
+      <c r="Q253" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R253" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T06:32:35.394958+00:00</t>
         </is>
       </c>
     </row>
@@ -18601,9 +18626,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M276" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M276" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N276" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-091263</t>
+        </is>
+      </c>
+      <c r="O276" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4755</t>
+        </is>
+      </c>
+      <c r="P276" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/16-17-tuoi-thue-xe-ga-50cc-dieu-59-luat-36-2024-cho-lai-dieu-21-va-586-bo-luat-dan-su-noi-gi-ve-cha-me/</t>
+        </is>
+      </c>
+      <c r="Q276" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R276" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T06:32:35.394958+00:00</t>
         </is>
       </c>
     </row>
@@ -33331,7 +33381,7 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" ht="23" customHeight="1">
@@ -33341,7 +33391,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="6" ht="23" customHeight="1">

--- a/editorial/title-plan-1482/seo-tieu-de-03-494.xlsx
+++ b/editorial/title-plan-1482/seo-tieu-de-03-494.xlsx
@@ -17554,9 +17554,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M260" s="0" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M260" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N260" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-091247</t>
+        </is>
+      </c>
+      <c r="O260" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4758</t>
+        </is>
+      </c>
+      <c r="P260" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/xem-tuoi-tho-pin-xe-may-dien-o-dau-app-vinfast-evo200-neu-6-chi-so-pin-dat-bike-co-man-hinh-ky-thuat/</t>
+        </is>
+      </c>
+      <c r="Q260" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R260" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T06:50:02.902014+00:00</t>
         </is>
       </c>
     </row>
@@ -30778,9 +30803,34 @@
           <t xml:space="preserve">4</t>
         </is>
       </c>
-      <c r="M457" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">PLANNED</t>
+      <c r="M457" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUBLISHED_G7_PASS</t>
+        </is>
+      </c>
+      <c r="N457" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NT-091444</t>
+        </is>
+      </c>
+      <c r="O457" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4759</t>
+        </is>
+      </c>
+      <c r="P457" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://thuexemaynguyentu.com/man-hinh-hmi-vinfast-drgnfly-sach-tieng-viet-ghi-3-muc-tro-luc-4-thong-so-10-ma-loi-ban-tieng-anh-ghi-gi/</t>
+        </is>
+      </c>
+      <c r="Q457" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PASS</t>
+        </is>
+      </c>
+      <c r="R457" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-22T06:50:02.902014+00:00</t>
         </is>
       </c>
     </row>
@@ -33381,7 +33431,7 @@
         </is>
       </c>
       <c r="B4" s="0" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" ht="23" customHeight="1">
@@ -33391,7 +33441,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
     <row r="6" ht="23" customHeight="1">
